--- a/resources/EegWorkflow_parameters.xlsx
+++ b/resources/EegWorkflow_parameters.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="1" max="2"/>
@@ -1121,309 +1121,309 @@
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>locs</t>
+          <t>use_ransac</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Locs file</t>
+          <t>Use RANSAC (PREP)</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>"Standard,Biosemi 64,Biosemi 128,Biosemi 128 (10/20 names),TDBrain,Brain Products 128,Temple Uni,EGI 128,EGI 128 (10/20 names)"</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n"/>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>Convert channel names for some systems and apply provided channel locations</t>
+          <t>Remove channels that their RANSAC prediction does not reproduce: each channel is predicted by spherical splines from random subsets of the other channels (median over the subsets), and a channel is removed when it correlates below the RANSAC r in more than the RANSAC max. bad time of the windows. PREP's bad-channel test (findNoisyChannels). Runs after the tests above, on located channels not named *eog*; PREP expects high-passed data</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>addref</t>
+          <t>ransac_r</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Add ref</t>
+          <t>RANSAC min. correlation r</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>"none,FPz,CPz,Cz"</t>
+          <t>min=.3,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>Add missing reference channel as flatline</t>
+          <t>A window is bad when the channel correlates less than this with its RANSAC prediction (PREP: 0.75)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>resample</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>srate</t>
+          <t>ransac_maxbad</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Sampling rate</t>
+          <t>RANSAC max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>"64,128,250,256,422,500,512,1000,1024,2048,4096"</t>
+          <t>min=.05,max=.9,by=.05</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>Target sampling rate in Hz (DISCOVER-EEG: 250)</t>
+          <t>A channel is removed when it is bad in more than this proportion of the recording (PREP: 0.4)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>resample</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>ransac_window</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>RANSAC window (s)</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>"pop_resample,spline"</t>
+          <t>min=1,max=20,by=1</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>Used for non-integer ratios only. pop_resample low-pass filters against aliasing (DISCOVER-EEG). spline interpolates the unfiltered data: faster, but aliases</t>
+          <t>Length of the non-overlapping windows in which the correlation is computed (PREP: 5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>pop_resample</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>rereference</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>refchans</t>
+          <t>ransac_draws</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Refernce to</t>
+          <t>RANSAC random subsets</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>"Average,CPz,M1/M2,REST,A1/A2,CSD,TP9/10,P9/10,E56/E57/E100/E107"</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Reference the data to this montage. Average excludes HEOG/VEOG; REST and CSD use the channel locations, so run Lookup first</t>
+          <t>min=10,max=200,by=10</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Number of random channel subsets the prediction is the median over (PREP: 50)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>rereference</t>
+          <t>excessive signal</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>interpremoved</t>
+          <t>ransac_fraction</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Include removed channels</t>
+          <t>RANSAC subset fraction</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="n"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Average only. Interpolates the channels removed earlier (with a location), computes the average over the full montage, then removes them again (DISCOVER-EEG)</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>min=.1,max=.5,by=.05</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Size of each random subset as a proportion of the channels (PREP: 0.25)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>lookup</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>locs</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Lower bound</t>
+          <t>Locs file</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=40,by=.5</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
+          <t>"Standard,Biosemi 64,Biosemi 128,Biosemi 128 (10/20 names),TDBrain,Brain Products 128,Temple Uni,EGI 128,EGI 128 (10/20 names)"</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Convert channel names for some systems and apply provided channel locations</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>lookup</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>addref</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Upper bound</t>
+          <t>Add ref</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>min=4,max=200,by=1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Low-pass cutoff in Hz. Keep it below half the sampling rate</t>
+          <t>"none,FPz,CPz,Cz"</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Add missing reference channel as flatline</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>resample</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>srate</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Sampling rate</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1433,252 +1433,252 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>"FIR,Butterworth"</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
+          <t>"64,128,250,256,422,500,512,1000,1024,2048,4096"</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Target sampling rate in Hz (DISCOVER-EEG: 250)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FIR</t>
+          <t>250</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>resample</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>transition_hp</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Highpass transition (Hz)</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=4,by=.25</t>
+          <t>"pop_resample,spline"</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
+          <t>Used for non-integer ratios only. pop_resample low-pass filters against aliasing (DISCOVER-EEG). spline interpolates the unfiltered data: faster, but aliases</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>pop_resample</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>transition_lp</t>
+          <t>refchans</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Lowpass transition (Hz)</t>
+          <t>Refernce to</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=10,by=.25</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
+          <t>"Average,CPz,M1/M2,REST,A1/A2,CSD,TP9/10,P9/10,E56/E57/E100/E107"</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Reference the data to this montage. Average excludes HEOG/VEOG; REST and CSD use the channel locations, so run Lookup first</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>interpremoved</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Include removed channels</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>"eeg_linenoise,CleanLine"</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise: sinusoids of estimated frequency regressed out of all channels at once (fast). CleanLine: the EEGLAB plugin in 4 s sliding windows, as in DISCOVER-EEG</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="n"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Average only. Interpolates the channels removed earlier (with a location), computes the average over the full montage, then removes them again (DISCOVER-EEG)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>eeg_linenoise</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>linefreq</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Line frequency (Hz)</t>
+          <t>Lower bound</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>"50,60"</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
+          <t>min=0,max=40,by=.5</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>harmonics</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>All harmonics</t>
+          <t>Upper bound</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>min=4,max=200,by=1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Low-pass cutoff in Hz. Keep it below half the sampling rate</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>segmentlength</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Piece length (s)</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>min=5,max=120,by=5</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise only: the line frequency is re-estimated per piece of this many seconds, because mains frequency drifts. 20 s removed the 60 Hz peak fully in tests; the whole recording at once removed almost nothing</t>
+          <t>"FIR,Butterworth"</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>FIR</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>minpeak</t>
+          <t>transition_hp</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Min. peak (dB)</t>
+          <t>Highpass transition (Hz)</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1688,34 +1688,34 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=20,by=.5</t>
+          <t>min=.25,max=4,by=.25</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
+          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>winlen</t>
+          <t>transition_lp</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Window length</t>
+          <t>Lowpass transition (Hz)</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -1725,145 +1725,141 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>min=10,max=120,by=10</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
+          <t>min=.25,max=10,by=.25</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>winshift</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Window shift</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>min=5,max=60,by=5</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
+          <t>"eeg_linenoise,CleanLine"</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise: sinusoids of estimated frequency regressed out of all channels at once (fast). CleanLine: the EEGLAB plugin in 4 s sliding windows, as in DISCOVER-EEG</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>eeg_linenoise</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>alt emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>linefreq</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Tstat</t>
+          <t>Line frequency (Hz)</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>min=1,max=8,by=.5</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
+          <t>"50,60"</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>alt eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>harmonics</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Threshold r</t>
+          <t>All harmonics</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n"/>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>segmentlength</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Threshold %</t>
+          <t>Piece length (s)</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -1873,71 +1869,67 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
+          <t>min=2,max=120,by=1</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: each stretch between boundaries is split into equal pieces of about this many seconds, and the line frequency is estimated per piece, because the mains frequency wanders (HBN: ~0.02 Hz over 20-60 s plus small wiggles). 5 s with the drift fit on follows it best; longer pieces keep more brain signal right at the line frequency</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>burstcriterion</t>
+          <t>drift</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Burst criterion</t>
+          <t>Fit frequency drift</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>min=0,max=40,by=1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n"/>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: per piece, fit the line frequency as drifting linearly over the piece (frequency plus drift rate) instead of constant. Never fits worse than a constant frequency; about 4x slower (still well under a second per minute of data)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>chanminr</t>
+          <t>minpeak</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Channel min. r</t>
+          <t>Min. peak (dB)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1947,34 +1939,34 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
+          <t>min=0,max=20,by=.5</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>winlen</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Window length</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -1984,103 +1976,108 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>min=.1,max=.8,by=.05</t>
+          <t>min=10,max=120,by=10</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
+          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>burstdelete</t>
+          <t>winshift</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Remove bursts</t>
+          <t>Window shift</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>min=5,max=60,by=5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
+          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>asr</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>burstmergegap</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Remove burst merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>alt emg</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Tstat</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>min=1,max=8,by=.5</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
+          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>alt eog</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>flatline</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Flatline (s)</t>
+          <t>Threshold r</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -2088,36 +2085,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>min=0,max=60,by=1</t>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
+          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>eog</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Line noise (SD)</t>
+          <t>Threshold %</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -2125,19 +2122,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
+          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2149,27 +2146,32 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>burstcriterion</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Drift highpass 0.25-0.75 Hz</t>
+          <t>Burst criterion</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=40,by=1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
+          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2183,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>windowcriterion</t>
+          <t>chanminr</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Window criterion</t>
+          <t>Channel min. r</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -2194,36 +2196,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>pca</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Initial PCA</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -2233,34 +2235,34 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>min=16,max=250,by=1</t>
+          <t>min=.1,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
+          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>use_muscle</t>
+          <t>burstdelete</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Remove Muscle</t>
+          <t>Remove bursts</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -2268,102 +2270,105 @@
           <t>checkbox</t>
         </is>
       </c>
-      <c r="E51" s="1" t="n"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>muscle</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>Muscle probability</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>asr</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>burstmergegap</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remove burst merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
+          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>use_eye</t>
+          <t>flatline</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Remove Eye</t>
+          <t>Flatline (s)</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=1</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Eye probability</t>
+          <t>Line noise (SD)</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -2371,36 +2376,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
+          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>use_heart</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Remove Heart</t>
+          <t>Drift highpass 0.25-0.75 Hz</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -2408,32 +2413,31 @@
           <t>checkbox</t>
         </is>
       </c>
-      <c r="E55" s="1" t="n"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>windowcriterion</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Heart probability</t>
+          <t>Window criterion</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -2441,19 +2445,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
+          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -2465,28 +2469,32 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>use_linenoise</t>
+          <t>pca</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Remove Line Noise</t>
+          <t>Initial PCA</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>min=16,max=250,by=1</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -2498,32 +2506,28 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>use_muscle</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Line Noise probability</t>
+          <t>Remove Muscle</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2535,28 +2539,32 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>use_channoise</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Remove Channel Noise</t>
+          <t>Muscle probability</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2568,32 +2576,28 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>channoise</t>
+          <t>use_eye</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Channel Noise probability</t>
+          <t>Remove Eye</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="n"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2605,28 +2609,32 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>use_other</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Remove Other</t>
+          <t>Eye probability</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2638,32 +2646,28 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>use_heart</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Other probability</t>
+          <t>Remove Heart</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="n"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2679,12 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>repburst</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: burst (SD)</t>
+          <t>Heart probability</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2688,19 +2692,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>min=5,max=40,by=1</t>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2712,32 +2716,28 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>repwindow</t>
+          <t>use_linenoise</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: window</t>
+          <t>Remove Line Noise</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="n"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2749,184 +2749,189 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>discovereeg</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>DISCOVER-EEG: remove bad segments</t>
+          <t>Line Noise probability</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>use_channoise</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Remove Channel Noise</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
           <t>checkbox</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="E66" s="1" t="n"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>channoise</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Channel Noise probability</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>use_other</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Remove Other</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="n"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>min=.5,max=4,by=.5</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Other probability</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
+          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>repburst</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>highpass (low bound) Hz</t>
+          <t>Bad segments: burst (SD)</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
@@ -2934,34 +2939,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>min=10,max=40,by=5</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>Highpass for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>20</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>min=5,max=40,by=1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>lowpass</t>
+          <t>repwindow</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>lowpass (upper bound) Hz</t>
+          <t>Bad segments: window</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2969,193 +2976,192 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>min=30,max=120,by=5</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>Lowpass frequency for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>40</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>discovereeg</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>DISCOVER-EEG: remove bad segments</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>dBcriterion</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>Use dB test</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="n"/>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>epochlen</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Epoch length (s)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>min=.5,max=4,by=.5</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>Criterion (dB)</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>min=-20,max=0,by=.5</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Epoch overlap (prop.)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>min=0,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>doPsdSlope</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>Use slope test</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="n"/>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>slopeCriterionAbsolute</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>Slope above (dB/Hz)</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>slopeCriterionInterpolationDelta</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>Slope minus interp. (dB/Hz)</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>mergegap</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>min=0,max=5,by=.5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3166,29 +3172,31 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>zP</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Use z-score p-value threshold</t>
+          <t>highpass (low bound) Hz</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>min=10,max=40,by=5</t>
+        </is>
+      </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Highpass for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="78">
@@ -3199,12 +3207,12 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>zPvalue</t>
+          <t>lowpass</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>p-value below</t>
+          <t>lowpass (upper bound) Hz</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -3214,18 +3222,16 @@
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>min=.0001,max=.05,by=.0001</t>
+          <t>min=30,max=120,by=5</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
+          <t>Lowpass frequency for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -3236,12 +3242,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>zFDR</t>
+          <t>dBcriterion</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Use z-score FDR threshold</t>
+          <t>Use dB test</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -3252,12 +3258,12 @@
       <c r="E79" s="1" t="n"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3275,12 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>zFDRalpha</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>FDR q</t>
+          <t>Criterion (dB)</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -3284,314 +3290,314 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=-20,max=0,by=.5</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>False discovery rate (q) for the z-score FDR threshold</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>doPsdSlope</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Use slope test</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="n"/>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionAbsolute</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Slope above (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionInterpolationDelta</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Slope minus interp. (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>zP</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score p-value threshold</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="n"/>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>zPvalue</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>p-value below</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>min=.0001,max=.05,by=.0001</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>zFDR</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="n"/>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>zFDRalpha</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>FDR q</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>min=.001,max=.1,by=.001</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>False discovery rate (q) for the z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
           <t>flat periods</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>epochlen</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Epoch length (s)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>min=.05,max=2,by=.05</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="G88" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>SD below (uV)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>min=.05,max=5,by=.05</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>An epoch is flat in a channel when its detrended SD is below this</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>min=.5,max=10,by=.5</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,32 +3607,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FDR alpha</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3636,32 +3642,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
+          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>maxamp</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Max. amplitude (uV)</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3671,32 +3677,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>min=50,max=2000,by=50</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>epochlen</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Epoch length (s)</t>
+          <t>SD below (uV)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3706,32 +3712,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>min=.5,max=10,by=.5</t>
+          <t>min=.05,max=5,by=.05</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Length of the epochs the data are cut into</t>
+          <t>An epoch is flat in a channel when its detrended SD is below this</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>overlap</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Epoch overlap (prop.)</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3741,32 +3747,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>min=0,max=.9,by=.1</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Proportion of overlap between successive epochs</t>
+          <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3776,32 +3782,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3811,32 +3817,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>sdcrit</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SD of difference</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3846,32 +3852,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>min=2,max=30,by=1</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>rcrit</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Min. correlation r</t>
+          <t>FDR alpha</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3881,32 +3887,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>min=-1,max=.9,by=.05</t>
+          <t>min=.001,max=.1,by=.001</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>task periods</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>maxamp</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seconds before event</t>
+          <t>Max. amplitude (uV)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3916,52 +3922,408 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>min=0,max=60,by=.5</t>
+          <t>min=50,max=2000,by=50</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>"Leave-one-out,RANSAC"</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>How each channel's interpolation is computed. Leave-one-out: spherical splines from all other channels. RANSAC: median of the spherical-spline predictions from random channel subsets (as PREP), robust against other bad channels nearby. The tests below are the same for both</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Leave-one-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>epochlen</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Epoch length (s)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>min=.5,max=10,by=.5</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Length of the epochs the data are cut into</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Epoch overlap (prop.)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>min=0,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mergegap</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>min=0,max=5,by=.5</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sdcrit</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SD of difference</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>min=2,max=30,by=1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>rcrit</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Min. correlation r</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>min=-1,max=.9,by=.05</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ransac_draws</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>RANSAC random subsets</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>min=10,max=200,by=10</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ransac_fraction</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>RANSAC subset fraction</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>min=.1,max=.5,by=.05</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>task periods</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Seconds before event</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=.5</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>task periods</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Seconds after event</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>min=0,max=600,by=.5</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>End of a task period, in seconds after each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/resources/EegWorkflow_parameters.xlsx
+++ b/resources/EegWorkflow_parameters.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="1" max="2"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>"Leave-one-out,RANSAC"</t>
+          <t>"Leave-one-out,RANSAC,Autoreject"</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>How each channel's interpolation is computed. Leave-one-out: spherical splines from all other channels. RANSAC: median of the spherical-spline predictions from random channel subsets (as PREP), robust against other bad channels nearby. The tests below are the same for both</t>
+          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4258,17 +4258,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>task periods</t>
+          <t>interpolation clean</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>ar_folds</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seconds before event</t>
+          <t>Autoreject folds</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>min=0,max=60,by=.5</t>
+          <t>min=3,max=20,by=1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4300,30 +4300,67 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Seconds before event</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=.5</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>task periods</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>after</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Seconds after event</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>min=0,max=600,by=.5</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>End of a task period, in seconds after each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/resources/EegWorkflow_parameters.xlsx
+++ b/resources/EegWorkflow_parameters.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="1" max="2"/>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>"Average,CPz,M1/M2,REST,A1/A2,CSD,TP9/10,P9/10,E56/E57/E100/E107"</t>
+          <t>"Average,Robust average (PREP),CPz,M1/M2,REST,A1/A2,CSD,TP9/10,P9/10,E56/E57/E100/E107"</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reference the data to this montage. Average excludes HEOG/VEOG; REST and CSD use the channel locations, so run Lookup first</t>
+          <t>Reference of the data. Average: mean over all channels. Robust average (PREP): the mean over channels with the bad channels interpolated first, repeated until the set of bad channels is stable (eeg_robustref), so that one noisy channel does not leak into all the others. The other entries reference to those electrodes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>robustiter</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Lower bound</t>
+          <t>Robust: iterations</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1577,34 +1577,34 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=40,by=.5</t>
+          <t>min=1,max=10,by=1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
+          <t>Maximum number of detect/reference rounds of the robust average reference (PREP: 4)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>robustdev</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Upper bound</t>
+          <t>Robust: deviation z</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -1614,71 +1614,71 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>min=4,max=200,by=1</t>
+          <t>min=0,max=10,by=.5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Low-pass cutoff in Hz. Keep it below half the sampling rate</t>
+          <t>A channel whose SD is this many robust z from the median is bad. 0 = off (PREP: 5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>robustcorr</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Robust: min. correlation</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>"FIR,Butterworth"</t>
+          <t>min=0,max=.9,by=.05</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
+          <t>A channel correlating less than this with every other channel, in more than 1% of the 1 s windows, is bad. 0 = off (PREP: 0.4)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FIR</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>transition_hp</t>
+          <t>robusthf</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Highpass transition (Hz)</t>
+          <t>Robust: HF noise z</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1688,248 +1688,248 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=4,by=.25</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
+          <t>min=0,max=10,by=.5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>A channel whose noise above 45 Hz relative to its signal is this many robust z from the median is bad. 0 = off (PREP: 5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>transition_lp</t>
+          <t>robustransac</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Lowpass transition (Hz)</t>
+          <t>Robust: use RANSAC</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>min=.25,max=10,by=.25</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Also use the RANSAC test (as in Bad chans) to find bad channels for the robust average reference (PREP: on)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>robustinterp</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Robust: keep interpolated</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>"eeg_linenoise,CleanLine"</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise: sinusoids of estimated frequency regressed out of all channels at once (fast). CleanLine: the EEGLAB plugin in 4 s sliding windows, as in DISCOVER-EEG</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Leave the bad channels in the data as their interpolation (PREP does this). Off: they keep their own signal minus the reference</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>eeg_linenoise</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>linefreq</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Line frequency (Hz)</t>
+          <t>Lower bound</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>"50,60"</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
+          <t>min=0,max=40,by=.5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>harmonics</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>All harmonics</t>
+          <t>Upper bound</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="n"/>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>min=4,max=200,by=1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Low-pass cutoff in Hz. Keep it below half the sampling rate</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>segmentlength</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Piece length (s)</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>min=2,max=120,by=1</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise only: each stretch between boundaries is split into equal pieces of about this many seconds, and the line frequency is estimated per piece, because the mains frequency wanders (HBN: ~0.02 Hz over 20-60 s plus small wiggles). 5 s with the drift fit on follows it best; longer pieces keep more brain signal right at the line frequency</t>
+          <t>"FIR,Butterworth"</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>FIR</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>drift</t>
+          <t>transition_hp</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Fit frequency drift</t>
+          <t>Highpass transition (Hz)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=4,by=.25</t>
+        </is>
+      </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>eeg_linenoise only: per piece, fit the line frequency as drifting linearly over the piece (frequency plus drift rate) instead of constant. Never fits worse than a constant frequency; about 4x slower (still well under a second per minute of data)</t>
+          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>minpeak</t>
+          <t>transition_lp</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Min. peak (dB)</t>
+          <t>Lowpass transition (Hz)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1939,145 +1939,141 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=20,by=.5</t>
+          <t>min=.25,max=10,by=.25</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
+          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>winlen</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Window length</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>min=10,max=120,by=10</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
+          <t>"eeg_linenoise,CleanLine"</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise: sinusoids of estimated frequency regressed out of all channels at once (fast). CleanLine: the EEGLAB plugin in 4 s sliding windows, as in DISCOVER-EEG</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>eeg_linenoise</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>winshift</t>
+          <t>linefreq</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Window shift</t>
+          <t>Line frequency (Hz)</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>min=5,max=60,by=5</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
+          <t>"50,60"</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>alt emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>harmonics</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Tstat</t>
+          <t>All harmonics</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>min=1,max=8,by=.5</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>alt eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>segmentlength</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Threshold r</t>
+          <t>Piece length (s)</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -2087,71 +2083,67 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
+          <t>min=2,max=120,by=1</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: each stretch between boundaries is split into equal pieces of about this many seconds, and the line frequency is estimated per piece, because the mains frequency wanders (HBN: ~0.02 Hz over 20-60 s plus small wiggles). 5 s with the drift fit on follows it best; longer pieces keep more brain signal right at the line frequency</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>drift</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Threshold %</t>
+          <t>Fit frequency drift</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n"/>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: per piece, fit the line frequency as drifting linearly over the piece (frequency plus drift rate) instead of constant. Never fits worse than a constant frequency; about 4x slower (still well under a second per minute of data)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>burstcriterion</t>
+          <t>minpeak</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Burst criterion</t>
+          <t>Min. peak (dB)</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -2161,34 +2153,34 @@
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=40,by=1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
+          <t>min=0,max=20,by=.5</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>chanminr</t>
+          <t>winlen</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Channel min. r</t>
+          <t>Window length</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -2198,34 +2190,34 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=.95,by=.05</t>
+          <t>min=10,max=120,by=10</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
+          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>winshift</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Window shift</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -2235,103 +2227,108 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>min=.1,max=.8,by=.05</t>
+          <t>min=5,max=60,by=5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
+          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>alt emg</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>burstdelete</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Remove bursts</t>
+          <t>Tstat</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>min=1,max=8,by=.5</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
+          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>asr</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>burstmergegap</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remove burst merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>alt eog</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Threshold r</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
+          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>eog</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>flatline</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Flatline (s)</t>
+          <t>Threshold %</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -2339,19 +2336,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>min=0,max=60,by=1</t>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
+          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2360,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>burstcriterion</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Line noise (SD)</t>
+          <t>Burst criterion</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -2376,19 +2373,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=40,by=1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
+          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2400,27 +2397,32 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>chanminr</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Drift highpass 0.25-0.75 Hz</t>
+          <t>Channel min. r</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
+          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2434,12 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>windowcriterion</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Window criterion</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -2445,106 +2447,105 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>min=.1,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>pca</t>
+          <t>burstdelete</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Initial PCA</t>
+          <t>Remove bursts</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>min=16,max=250,by=1</t>
+          <t>checkbox</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
+          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>use_muscle</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>Remove Muscle</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="n"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>asr</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>burstmergegap</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remove burst merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>muscle</t>
+          <t>flatline</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Muscle probability</t>
+          <t>Flatline (s)</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -2552,122 +2553,125 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
+          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>use_eye</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Remove Eye</t>
+          <t>Line noise (SD)</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Eye probability</t>
+          <t>Drift highpass 0.25-0.75 Hz</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+          <t>checkbox</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
+          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>use_heart</t>
+          <t>windowcriterion</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Remove Heart</t>
+          <t>Window criterion</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2683,12 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>pca</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Heart probability</t>
+          <t>Initial PCA</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2694,17 +2698,17 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>min=.4,max=.9,by=.1</t>
+          <t>min=16,max=250,by=1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
+          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2720,12 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>use_linenoise</t>
+          <t>use_muscle</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Remove Line Noise</t>
+          <t>Remove Muscle</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -2732,7 +2736,7 @@
       <c r="E64" s="1" t="n"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2749,12 +2753,12 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Line Noise probability</t>
+          <t>Muscle probability</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -2769,7 +2773,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2786,12 +2790,12 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>use_channoise</t>
+          <t>use_eye</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Remove Channel Noise</t>
+          <t>Remove Eye</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -2802,7 +2806,7 @@
       <c r="E66" s="1" t="n"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2819,12 +2823,12 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>channoise</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Channel Noise probability</t>
+          <t>Eye probability</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -2839,7 +2843,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2856,12 +2860,12 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>use_other</t>
+          <t>use_heart</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Remove Other</t>
+          <t>Remove Heart</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
@@ -2872,12 +2876,12 @@
       <c r="E68" s="1" t="n"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2893,12 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Other probability</t>
+          <t>Heart probability</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -2909,7 +2913,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2926,32 +2930,28 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>repburst</t>
+          <t>use_linenoise</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: burst (SD)</t>
+          <t>Remove Line Noise</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>min=5,max=40,by=1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="n"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2963,12 +2963,12 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>repwindow</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: window</t>
+          <t>Line Noise probability</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2976,19 +2976,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>discovereeg</t>
+          <t>use_channoise</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>DISCOVER-EEG: remove bad segments</t>
+          <t>Remove Channel Noise</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -3013,171 +3013,176 @@
           <t>checkbox</t>
         </is>
       </c>
+      <c r="E72" s="1" t="n"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
+          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>channoise</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Channel Noise probability</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>use_other</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Remove Other</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="n"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>min=.5,max=4,by=.5</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Other probability</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>0.4</v>
+          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>repburst</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Bad segments: burst (SD)</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=5,max=40,by=1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
+          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>repwindow</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>highpass (low bound) Hz</t>
+          <t>Bad segments: window</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -3185,191 +3190,192 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>min=10,max=40,by=5</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>Highpass for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>20</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>discovereeg</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>DISCOVER-EEG: remove bad segments</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>lowpass</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>lowpass (upper bound) Hz</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>min=30,max=120,by=5</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>Lowpass frequency for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>epochlen</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Epoch length (s)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>min=.5,max=4,by=.5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>dBcriterion</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>Use dB test</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="n"/>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Epoch overlap (prop.)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>min=0,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>Criterion (dB)</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>min=-20,max=0,by=.5</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>doPsdSlope</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>Use slope test</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="n"/>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>slopeCriterionAbsolute</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>Slope above (dB/Hz)</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>mergegap</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>min=0,max=5,by=.5</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3380,12 +3386,12 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>slopeCriterionInterpolationDelta</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Slope minus interp. (dB/Hz)</t>
+          <t>highpass (low bound) Hz</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
@@ -3395,18 +3401,16 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>min=-2,max=2,by=.05</t>
+          <t>min=10,max=40,by=5</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>Highpass for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -3417,29 +3421,31 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>zP</t>
+          <t>lowpass</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Use z-score p-value threshold</t>
+          <t>lowpass (upper bound) Hz</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>min=30,max=120,by=5</t>
+        </is>
+      </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Lowpass frequency for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -3450,32 +3456,28 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>zPvalue</t>
+          <t>dBcriterion</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>p-value below</t>
+          <t>Use dB test</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>min=.0001,max=.05,by=.0001</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="n"/>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
+          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3487,29 +3489,31 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>zFDR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Use z-score FDR threshold</t>
+          <t>Criterion (dB)</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>min=-20,max=0,by=.5</t>
+        </is>
+      </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="87">
@@ -3520,294 +3524,294 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>zFDRalpha</t>
+          <t>doPsdSlope</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>FDR q</t>
+          <t>Use slope test</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>min=.001,max=.1,by=.001</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="n"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>False discovery rate (q) for the z-score FDR threshold</t>
+          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionAbsolute</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Slope above (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionInterpolationDelta</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Slope minus interp. (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>zP</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score p-value threshold</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="n"/>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>zPvalue</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>p-value below</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>min=.0001,max=.05,by=.0001</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>zFDR</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="n"/>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>zFDRalpha</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>FDR q</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>min=.001,max=.1,by=.001</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>False discovery rate (q) for the z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
           <t>flat periods</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>epochlen</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Epoch length (s)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>min=.05,max=2,by=.05</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
-      <c r="G88" t="n">
+      <c r="G94" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SD below (uV)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>min=.05,max=5,by=.05</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>An epoch is flat in a channel when its detrended SD is below this</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>min=.5,max=10,by=.5</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3817,32 +3821,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3852,32 +3856,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FDR alpha</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3887,32 +3891,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>maxamp</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Max. amplitude (uV)</t>
+          <t>SD below (uV)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3922,69 +3926,67 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>min=50,max=2000,by=50</t>
+          <t>min=.05,max=5,by=.05</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+          <t>An epoch is flat in a channel when its detrended SD is below this</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>400</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>"Leave-one-out,RANSAC,Autoreject"</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Leave-one-out</t>
-        </is>
+          <t>Length of the epochs the data are cut into</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>epochlen</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Epoch length (s)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3994,32 +3996,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>min=.5,max=10,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Length of the epochs the data are cut into</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>overlap</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Epoch overlap (prop.)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4029,32 +4031,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>min=0,max=.9,by=.1</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Proportion of overlap between successive epochs</t>
+          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4064,32 +4066,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>FDR alpha</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4099,32 +4101,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=.001,max=.1,by=.001</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>sdcrit</t>
+          <t>maxamp</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SD of difference</t>
+          <t>Max. amplitude (uV)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4134,16 +4136,16 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>min=2,max=30,by=1</t>
+          <t>min=50,max=2000,by=50</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105">
@@ -4154,31 +4156,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>rcrit</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Min. correlation r</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>min=-1,max=.9,by=.05</t>
+          <t>"Leave-one-out,RANSAC,Autoreject"</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
+          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Leave-one-out</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -4189,12 +4193,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ransac_draws</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RANSAC random subsets</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4204,18 +4208,16 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>min=10,max=200,by=10</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>Length of the epochs the data are cut into</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4226,12 +4228,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ransac_fraction</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RANSAC subset fraction</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4241,18 +4243,16 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>min=.1,max=.5,by=.05</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="108">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ar_folds</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Autoreject folds</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4278,34 +4278,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>min=3,max=20,by=1</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>task periods</t>
+          <t>interpolation clean</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seconds before event</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4315,52 +4313,268 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>min=0,max=60,by=.5</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>sdcrit</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SD of difference</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>min=2,max=30,by=1</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>rcrit</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Min. correlation r</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>min=-1,max=.9,by=.05</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ransac_draws</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>RANSAC random subsets</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>min=10,max=200,by=10</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ransac_fraction</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RANSAC subset fraction</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>min=.1,max=.5,by=.05</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ar_folds</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Autoreject folds</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>min=3,max=20,by=1</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>task periods</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Seconds before event</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=.5</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>task periods</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Seconds after event</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>min=0,max=600,by=.5</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>End of a task period, in seconds after each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/resources/EegWorkflow_parameters.xlsx
+++ b/resources/EegWorkflow_parameters.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="1" max="2"/>
@@ -1743,23 +1743,27 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>robustinterp</t>
+          <t>robustcorrwin</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Robust: keep interpolated</t>
+          <t>Robust: correlation window (s)</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>min=.5,max=10,by=.5</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leave the bad channels in the data as their interpolation (PREP does this). Off: they keep their own signal minus the reference</t>
+          <t>Length of the windows the correlation test uses (PREP: 1)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1771,17 +1775,17 @@
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>robustbadtime</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Lower bound</t>
+          <t>Robust: bad time (prop.)</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1791,34 +1795,34 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=40,by=.5</t>
+          <t>min=.005,max=.5,by=.005</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
+          <t>Proportion of those windows a channel may fail the correlation test before it is bad (PREP: 0.01)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>robustransac_r</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Upper bound</t>
+          <t>Robust: RANSAC min. r</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -1828,71 +1832,71 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>min=4,max=200,by=1</t>
+          <t>min=.3,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Low-pass cutoff in Hz. Keep it below half the sampling rate</t>
+          <t>A RANSAC window is bad when the channel correlates less than this with its prediction (PREP: 0.75)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>robustransac_maxbad</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Robust: RANSAC max. bad time</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>"FIR,Butterworth"</t>
+          <t>min=.05,max=.9,by=.05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
+          <t>Proportion of the RANSAC windows a channel may fail before it is bad (PREP: 0.4)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FIR</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>transition_hp</t>
+          <t>robustransac_window</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Highpass transition (Hz)</t>
+          <t>Robust: RANSAC window (s)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1902,34 +1906,34 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=4,by=.25</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
+          <t>min=1,max=20,by=1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Length of the RANSAC windows (PREP: 5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>transition_lp</t>
+          <t>robustransac_draws</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Lowpass transition (Hz)</t>
+          <t>Robust: RANSAC subsets</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1939,141 +1943,141 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=10,by=.25</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
+          <t>min=10,max=200,by=10</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Number of random channel subsets the RANSAC prediction is the median over (PREP: 50)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>robustransac_fraction</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Robust: RANSAC subset fraction</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>"eeg_linenoise,CleanLine"</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise: sinusoids of estimated frequency regressed out of all channels at once (fast). CleanLine: the EEGLAB plugin in 4 s sliding windows, as in DISCOVER-EEG</t>
+          <t>min=.1,max=.5,by=.05</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Size of each random subset as a proportion of the channels (PREP: 0.25)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>eeg_linenoise</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>rereference</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>linefreq</t>
+          <t>robustinterp</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Line frequency (Hz)</t>
+          <t>Robust: keep interpolated</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>dropdown</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>"50,60"</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Leave the bad channels in the data as their interpolation (PREP does this). Off: they keep their own signal minus the reference</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>harmonics</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>All harmonics</t>
+          <t>Lower bound</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="n"/>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=40,by=.5</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>High-pass cutoff in Hz. 0 disables the high-pass. 1 Hz is usual before ICA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>segmentlength</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Piece length (s)</t>
+          <t>Upper bound</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -2083,67 +2087,71 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>min=2,max=120,by=1</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise only: each stretch between boundaries is split into equal pieces of about this many seconds, and the line frequency is estimated per piece, because the mains frequency wanders (HBN: ~0.02 Hz over 20-60 s plus small wiggles). 5 s with the drift fit on follows it best; longer pieces keep more brain signal right at the line frequency</t>
+          <t>min=0,max=200,by=1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Low-pass cutoff in Hz. 0 disables the low-pass (high-pass only). Keep it below half the sampling rate</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>drift</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Fit frequency drift</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>eeg_linenoise only: per piece, fit the line frequency as drifting linearly over the piece (frequency plus drift rate) instead of constant. Never fits worse than a constant frequency; about 4x slower (still well under a second per minute of data)</t>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>"FIR,Butterworth"</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FIR: linear phase windowed sinc (pop_eegfiltnew), sharpness set by the transition bandwidth. Butterworth: zero-phase IIR (filtfilt), order 4, edges at -6 dB</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FIR</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>cleanline</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>minpeak</t>
+          <t>transition_hp</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Min. peak (dB)</t>
+          <t>Highpass transition (Hz)</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -2153,34 +2161,34 @@
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=20,by=.5</t>
+          <t>min=.25,max=4,by=.25</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
+          <t>FIR only. Width of the band (Hz) over which the highpass goes from stop to pass, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at the cutoff</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>winlen</t>
+          <t>transition_lp</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Window length</t>
+          <t>Lowpass transition (Hz)</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -2190,145 +2198,141 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>min=10,max=120,by=10</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
+          <t>min=.25,max=10,by=.25</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>FIR only. Width of the band (Hz) over which the lowpass goes from pass to stop, centred on the cutoff. Narrower is sharper but gives a longer filter with more ringing. Capped at Nyquist</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>winshift</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Window shift</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>min=5,max=60,by=5</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
+          <t>"eeg_linenoise,CleanLine (fast),CleanLine (plugin)"</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise: one sinusoid of estimated frequency (with drift) per piece, regressed out of all channels at once. CleanLine (fast): CleanLine's own algorithm - a multitaper F-test in 4 s sliding windows, repeated - but with every channel done at once (eeg_cleanlinefast); same result as the plugin, about 6-9x faster. CleanLine (plugin): the EEGLAB plugin itself, the slowest but the reference implementation</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>CleanLine (fast)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>alt emg</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>linefreq</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Tstat</t>
+          <t>Line frequency (Hz)</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>min=1,max=8,by=.5</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
+          <t>"50,60"</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Mains frequency (Europe 50, Americas 60). Its 2nd to 4th harmonics below Nyquist are removed too, as in DISCOVER-EEG</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>alt eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>harmonics</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Threshold r</t>
+          <t>All harmonics</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="n"/>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Remove every multiple of the line frequency below Nyquist instead of only the first four</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>eog</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>segmentlength</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Threshold %</t>
+          <t>Piece length (s)</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -2338,71 +2342,67 @@
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>min=.25,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
+          <t>min=2,max=120,by=1</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: each stretch between boundaries is split into equal pieces of about this many seconds, and the line frequency is estimated per piece, because the mains frequency wanders (HBN: ~0.02 Hz over 20-60 s plus small wiggles). 5 s with the drift fit on follows it best; longer pieces keep more brain signal right at the line frequency</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>burstcriterion</t>
+          <t>drift</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Burst criterion</t>
+          <t>Fit frequency drift</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>min=0,max=40,by=1</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="n"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: per piece, fit the line frequency as drifting linearly over the piece (frequency plus drift rate) instead of constant. Never fits worse than a constant frequency; about 4x slower (still well under a second per minute of data)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>cleanline</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>chanminr</t>
+          <t>minpeak</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Channel min. r</t>
+          <t>Min. peak (dB)</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -2412,34 +2412,34 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>min=0,max=.95,by=.05</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
+          <t>min=0,max=20,by=.5</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>eeg_linenoise only: a frequency is removed only where its spectral peak stands at least this far above the surrounding 1.5-5 Hz (real mains measured 6-22 dB; no line noise below 2 dB with 32+ channels)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>winlen</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Window length</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -2449,103 +2449,108 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>min=.1,max=.8,by=.05</t>
+          <t>min=10,max=120,by=10</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
+          <t>Length in seconds of the sliding window that BSS-CCA cleans muscle activity in</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>emg</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>burstdelete</t>
+          <t>winshift</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Remove bursts</t>
+          <t>Window shift</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>min=5,max=60,by=5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
+          <t>Step in seconds between successive AAR windows. Half the window length gives 50% overlap</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>asr</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>burstmergegap</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Remove burst merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>alt emg</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>Tstat</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>min=1,max=8,by=.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
+          <t>A channel is cleaned when its 13-35 Hz power exceeds the interpolated estimate by more than this t-value. Higher = more conservative</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>alt eog</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>flatline</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Flatline (s)</t>
+          <t>Threshold r</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -2553,36 +2558,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>min=0,max=60,by=1</t>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
+          <t>Remove an independent component when its correlation with an *EOG* channel reaches this value. Higher = fewer components removed</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>asr</t>
+          <t>eog</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Line noise (SD)</t>
+          <t>Threshold %</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -2590,19 +2595,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>min=0,max=10,by=.5</t>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>min=.25,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
+          <t>Remove an independent component when ICLabel calls it "Eye" with at least this probability</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2614,27 +2619,32 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>burstcriterion</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Drift highpass 0.25-0.75 Hz</t>
+          <t>Burst criterion</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=40,by=1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
+          <t>ASR burst criterion in SD. 0 = off. Lower is more aggressive (DISCOVER-EEG: 20 in the bad-segments pass, off in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2656,12 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>windowcriterion</t>
+          <t>chanminr</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Window criterion</t>
+          <t>Channel min. r</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
@@ -2659,36 +2669,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>min=0,max=.95,by=.05</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>A channel correlating less than this with its reconstruction from the others is removed. 0 = off (DISCOVER-EEG: 0.8 in the bad-channels pass)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>pca</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Initial PCA</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2698,34 +2708,34 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>min=16,max=250,by=1</t>
+          <t>min=.1,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
+          <t>Proportion of the recording a channel may fail the correlation or line-noise test before it is removed (clean_rawdata default and DISCOVER-EEG: 0.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>use_muscle</t>
+          <t>burstdelete</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Remove Muscle</t>
+          <t>Remove bursts</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -2733,102 +2743,105 @@
           <t>checkbox</t>
         </is>
       </c>
-      <c r="E64" s="1" t="n"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>Remove bad segments instead of correcting them with ASR (DISCOVER-EEG: on in the bad-segments pass)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>muscle</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Muscle probability</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>asr</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>burstmergegap</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remove burst merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
+          <t>After cleaning, remove every stretch of data shorter than this (s) between boundaries, or between a boundary and the start/end of the recording, e.g. left between removed bursts. 0 = off</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>use_eye</t>
+          <t>flatline</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Remove Eye</t>
+          <t>Flatline (s)</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=1</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>A channel flat for longer than this many seconds is removed. 0 = off (clean_rawdata default and DISCOVER-EEG: 5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Eye probability</t>
+          <t>Line noise (SD)</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -2836,36 +2849,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>min=0,max=10,by=.5</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
+          <t>A channel with more line noise than this many SD above the others is removed. 0 = off (DISCOVER-EEG: 4)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>use_heart</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Remove Heart</t>
+          <t>Drift highpass 0.25-0.75 Hz</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
@@ -2873,32 +2886,31 @@
           <t>checkbox</t>
         </is>
       </c>
-      <c r="E68" s="1" t="n"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>High-pass filter inside clean_rawdata, transition band 0.25-0.75 Hz (DISCOVER-EEG: on). Leave off if you use the Filter step</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>windowcriterion</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Heart probability</t>
+          <t>Window criterion</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -2906,19 +2918,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
+          <t>A window is removed when more than this proportion of channels is bad in it. 0 = off (DISCOVER-EEG: 0.25)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -2930,28 +2942,32 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>use_linenoise</t>
+          <t>pca</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Remove Line Noise</t>
+          <t>Initial PCA</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>min=16,max=250,by=1</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -2963,32 +2979,28 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>extended</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Line Noise probability</t>
+          <t>Extended Infomax</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="n"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+          <t>Run extended Infomax (Lee, Girolami &amp; Sejnowski 1999): the sign of each component's kurtosis is estimated, so sub-Gaussian sources (line noise, some artefacts) are separated as well. Only runica and binica have it; PICARD and AMICA use their own model and ignore it (Makoto's pipeline: on; DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3012,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>use_channoise</t>
+          <t>use_muscle</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Remove Channel Noise</t>
+          <t>Remove Muscle</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -3016,7 +3028,7 @@
       <c r="E72" s="1" t="n"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3033,12 +3045,12 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>channoise</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Channel Noise probability</t>
+          <t>Muscle probability</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
@@ -3053,7 +3065,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3070,12 +3082,12 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>use_other</t>
+          <t>use_eye</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Remove Other</t>
+          <t>Remove Eye</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
@@ -3086,12 +3098,12 @@
       <c r="E74" s="1" t="n"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3115,12 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Other probability</t>
+          <t>Eye probability</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -3123,7 +3135,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3140,32 +3152,28 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>repburst</t>
+          <t>use_heart</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: burst (SD)</t>
+          <t>Remove Heart</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>min=5,max=40,by=1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="n"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3185,12 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>repwindow</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: window</t>
+          <t>Heart probability</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -3190,19 +3198,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3222,12 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>discovereeg</t>
+          <t>use_linenoise</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>DISCOVER-EEG: remove bad segments</t>
+          <t>Remove Line Noise</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -3227,171 +3235,172 @@
           <t>checkbox</t>
         </is>
       </c>
+      <c r="E78" s="1" t="n"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
+          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>linenoise</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Line Noise probability</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>use_channoise</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Remove Channel Noise</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="n"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>channoise</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Channel Noise probability</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>use_other</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Remove Other</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="n"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>min=.5,max=4,by=.5</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>highpass</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>highpass (low bound) Hz</t>
+          <t>Other probability</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
@@ -3401,32 +3410,34 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>min=10,max=40,by=5</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>Highpass for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>20</v>
+          <t>min=.4,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>lowpass</t>
+          <t>repburst</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>lowpass (upper bound) Hz</t>
+          <t>Bad segments: burst (SD)</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -3434,226 +3445,229 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>min=30,max=120,by=5</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>Lowpass frequency for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>40</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>min=5,max=40,by=1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>EMG periods</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>dBcriterion</t>
+          <t>repwindow</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Use dB test</t>
+          <t>Bad segments: window</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="n"/>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>discovereeg</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>DISCOVER-EEG: remove bad segments</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>Criterion (dB)</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>min=-20,max=0,by=.5</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>epochlen</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Epoch length (s)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>min=.5,max=4,by=.5</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>doPsdSlope</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>Use slope test</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="n"/>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Epoch overlap (prop.)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>min=0,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>slopeCriterionAbsolute</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>Slope above (dB/Hz)</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>EMG periods</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>slopeCriterionInterpolationDelta</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>Slope minus interp. (dB/Hz)</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>zP</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>Use z-score p-value threshold</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="n"/>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>mergegap</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>min=0,max=5,by=.5</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3664,12 +3678,12 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>zPvalue</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>p-value below</t>
+          <t>highpass (low bound) Hz</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -3679,18 +3693,16 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>min=.0001,max=.05,by=.0001</t>
+          <t>min=10,max=40,by=5</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
+          <t>Highpass for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -3701,29 +3713,31 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>zFDR</t>
+          <t>lowpass</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Use z-score FDR threshold</t>
+          <t>lowpass (upper bound) Hz</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>min=30,max=120,by=5</t>
+        </is>
+      </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Lowpass frequency for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -3734,364 +3748,362 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>zFDRalpha</t>
+          <t>dBcriterion</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>FDR q</t>
+          <t>Use dB test</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>min=.001,max=.1,by=.001</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="n"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>False discovery rate (q) for the z-score FDR threshold</t>
+          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Criterion (dB)</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>min=-20,max=0,by=.5</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>doPsdSlope</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Use slope test</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="n"/>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionAbsolute</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>Slope above (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>slopeCriterionInterpolationDelta</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Slope minus interp. (dB/Hz)</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>zP</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score p-value threshold</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="n"/>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>zPvalue</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>p-value below</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>min=.0001,max=.05,by=.0001</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>zFDR</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="n"/>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>zFDRalpha</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>FDR q</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>min=.001,max=.1,by=.001</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>False discovery rate (q) for the z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
           <t>flat periods</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>epochlen</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Epoch length (s)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>min=.05,max=2,by=.05</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
-      <c r="G94" t="n">
+      <c r="G102" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>SD below (uV)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>min=.05,max=5,by=.05</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>An epoch is flat in a channel when its detrended SD is below this</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>min=.5,max=10,by=.5</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>excessive periods</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>mergegap</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Merge gap (s)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>min=0,max=5,by=.5</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FDR alpha</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4101,32 +4113,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>maxamp</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Max. amplitude (uV)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4136,69 +4148,67 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>min=50,max=2000,by=50</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>400</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>"Leave-one-out,RANSAC,Autoreject"</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Leave-one-out</t>
-        </is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>epochlen</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Epoch length (s)</t>
+          <t>SD below (uV)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4208,32 +4218,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>min=.5,max=10,by=.5</t>
+          <t>min=.05,max=5,by=.05</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Length of the epochs the data are cut into</t>
+          <t>An epoch is flat in a channel when its detrended SD is below this</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>overlap</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Epoch overlap (prop.)</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4243,32 +4253,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>min=0,max=.9,by=.1</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Proportion of overlap between successive epochs</t>
+          <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4278,32 +4288,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4313,32 +4323,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>sdcrit</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SD of difference</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4348,32 +4358,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>min=2,max=30,by=1</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>rcrit</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Min. correlation r</t>
+          <t>FDR alpha</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4383,32 +4393,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>min=-1,max=.9,by=.05</t>
+          <t>min=.001,max=.1,by=.001</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ransac_draws</t>
+          <t>maxamp</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RANSAC random subsets</t>
+          <t>Max. amplitude (uV)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4418,18 +4428,16 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>min=10,max=200,by=10</t>
+          <t>min=50,max=2000,by=50</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="113">
@@ -4440,32 +4448,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ransac_fraction</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RANSAC subset fraction</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>min=.1,max=.5,by=.05</t>
+          <t>"Leave-one-out,RANSAC,Autoreject"</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
+          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>Leave-one-out</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4485,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ar_folds</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Autoreject folds</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4492,34 +4500,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>min=3,max=20,by=1</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Length of the epochs the data are cut into</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>task periods</t>
+          <t>interpolation clean</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seconds before event</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4529,52 +4535,338 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>min=0,max=60,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>mergegap</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Merge gap (s)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>min=0,max=5,by=.5</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>sdcrit</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SD of difference</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>min=2,max=30,by=1</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>rcrit</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Min. correlation r</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>min=-1,max=.9,by=.05</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ransac_draws</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RANSAC random subsets</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>min=10,max=200,by=10</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ransac_fraction</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>RANSAC subset fraction</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>min=.1,max=.5,by=.05</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ar_folds</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Autoreject folds</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>min=3,max=20,by=1</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>task periods</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Seconds before event</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=.5</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>task periods</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Seconds after event</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>min=0,max=600,by=.5</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>End of a task period, in seconds after each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/resources/EegWorkflow_parameters.xlsx
+++ b/resources/EegWorkflow_parameters.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="1" max="2"/>
@@ -2937,17 +2937,17 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>pca</t>
+          <t>maxmem</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Initial PCA</t>
+          <t>Working memory (GB)</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
@@ -2955,36 +2955,36 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>min=16,max=250,by=1</t>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>min=0,max=16,by=0.5</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
+          <t>Memory clean_rawdata may use. Its own default is 64 MB, which cuts the data into many blocks and makes ASR about 3 times slower; 1 GB or more keeps it in a few blocks. ASR restarts its update grid at every block, so the cleaned data differ slightly between settings - neither is wrong, but a value is reproducible. 0 = leave it to clean_rawdata (its 64 MB; what DISCOVER-EEG gets)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>asr</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>extended</t>
+          <t>fastasr</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Extended Infomax</t>
+          <t>Fast ASR (deterministic)</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2992,10 +2992,9 @@
           <t>checkbox</t>
         </is>
       </c>
-      <c r="E71" s="1" t="n"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Run extended Infomax (Lee, Girolami &amp; Sejnowski 1999): the sign of each component's kurtosis is estimated, so sub-Gaussian sources (line noise, some artefacts) are separated as well. Only runica and binica have it; PICARD and AMICA use their own model and ignore it (Makoto's pipeline: on; DISCOVER-EEG: off)</t>
+          <t>Use asr_process_fast for the burst step: the same algorithm, but the covariance is computed where it is used instead of smoothing a channels x channels x samples series (12.6 GB for 129 channels and 190 s). Given the same update grid it matches clean_rawdata exactly (correlation 1.000000); it is about 22x faster than the plugin's default and, unlike it, does not depend on how much memory ASR was given. Off: the plugin's own ASR, which DISCOVER-EEG and PREP use</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3012,28 +3011,32 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>use_muscle</t>
+          <t>pca</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Remove Muscle</t>
+          <t>Initial PCA</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>min=16,max=250,by=1</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>Number of principal components ICA is run on. Capped at the number of channels with locations</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -3045,32 +3048,28 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>muscle</t>
+          <t>extended</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Muscle probability</t>
+          <t>Extended Infomax</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>min=.4,max=.9,by=.1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="n"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
+          <t>Run extended Infomax (Lee, Girolami &amp; Sejnowski 1999): the sign of each component's kurtosis is estimated, so sub-Gaussian sources (line noise, some artefacts) are separated as well. Only runica and binica have it; PICARD and AMICA use their own model and ignore it (Makoto's pipeline: on; DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3081,12 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>use_eye</t>
+          <t>use_muscle</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Remove Eye</t>
+          <t>Remove Muscle</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
@@ -3098,7 +3097,7 @@
       <c r="E74" s="1" t="n"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
+          <t>Remove components that ICLabel classifies as Muscle with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3115,12 +3114,12 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Eye probability</t>
+          <t>Muscle probability</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -3135,7 +3134,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
+          <t>Minimum ICLabel Muscle probability for removal, when Remove Muscle is on</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3152,12 +3151,12 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>use_heart</t>
+          <t>use_eye</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Remove Heart</t>
+          <t>Remove Eye</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -3168,7 +3167,7 @@
       <c r="E76" s="1" t="n"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Eye with at least the probability set below (DISCOVER-EEG: on, 0.8)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3185,12 +3184,12 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Heart probability</t>
+          <t>Eye probability</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -3205,7 +3204,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
+          <t>Minimum ICLabel Eye probability for removal, when Remove Eye is on</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3222,12 +3221,12 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>use_linenoise</t>
+          <t>use_heart</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Remove Line Noise</t>
+          <t>Remove Heart</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -3238,7 +3237,7 @@
       <c r="E78" s="1" t="n"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Heart with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3255,12 +3254,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>linenoise</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Line Noise probability</t>
+          <t>Heart probability</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -3275,7 +3274,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
+          <t>Minimum ICLabel Heart probability for removal, when Remove Heart is on</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3292,12 +3291,12 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>use_channoise</t>
+          <t>use_linenoise</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Remove Channel Noise</t>
+          <t>Remove Line Noise</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -3308,7 +3307,7 @@
       <c r="E80" s="1" t="n"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Line Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3325,12 +3324,12 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>channoise</t>
+          <t>linenoise</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Channel Noise probability</t>
+          <t>Line Noise probability</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -3345,7 +3344,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
+          <t>Minimum ICLabel Line Noise probability for removal, when Remove Line Noise is on</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3362,12 +3361,12 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>use_other</t>
+          <t>use_channoise</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Remove Other</t>
+          <t>Remove Channel Noise</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
@@ -3378,12 +3377,12 @@
       <c r="E82" s="1" t="n"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
+          <t>Remove components that ICLabel classifies as Channel Noise with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3394,12 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>channoise</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Other probability</t>
+          <t>Channel Noise probability</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
@@ -3415,7 +3414,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
+          <t>Minimum ICLabel Channel Noise probability for removal, when Remove Channel Noise is on</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3432,32 +3431,28 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>repburst</t>
+          <t>use_other</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: burst (SD)</t>
+          <t>Remove Other</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>min=5,max=40,by=1</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="n"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+          <t>Remove components that ICLabel classifies as Other with at least the probability set below (DISCOVER-EEG: off)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3464,12 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>repwindow</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Bad segments: window</t>
+          <t>Other probability</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
@@ -3482,19 +3477,19 @@
           <t>value</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>min=0,max=1,by=.05</t>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>min=.4,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+          <t>Minimum ICLabel Other probability for removal, when Remove Other is on</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -3506,98 +3501,102 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
+          <t>repburst</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Bad segments: burst (SD)</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>min=5,max=40,by=1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ASR burst criterion of the clean_rawdata bad-segment pass after component subtraction: picks the most representative run (ICA number above 1) and, with DISCOVER-EEG on, sets the segments removed (DISCOVER-EEG: 20)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>repwindow</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Bad segments: window</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>min=0,max=1,by=.05</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Window criterion of that bad-segment pass: fraction of channels allowed to be out of range in a window. 0 = off (DISCOVER-EEG: 0.25)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
           <t>discovereeg</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>DISCOVER-EEG: remove bad segments</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D88" s="1" t="inlineStr">
         <is>
           <t>checkbox</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>On: after the components are subtracted, also remove the bad segments that clean_rawdata finds with the burst and window criteria above (DISCOVER-EEG step 6); with ICA number above 1, those of the kept run. Off: no segments are removed; they are only used to choose the run in case multiple ICA runs were selected. For DISCOVER-EEG, also remove Eye and Muscle ICs at 0.8 (and switch the other classes off).</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>epochlen</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Epoch length (s)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>min=.5,max=4,by=.5</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3608,12 +3607,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3623,16 +3622,16 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=.5,max=4,by=.5</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Length of the epochs the data are cut into. With the slope test on, 2 s gives steadier slopes than 1 s</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3643,101 +3642,101 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Epoch overlap (prop.)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>min=0,max=.9,by=.1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Proportion of overlap between successive epochs</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>maxbadtime</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Max. bad time (prop.)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>min=.05,max=.8,by=.05</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>A channel with muscle activity in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>mergegap</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Merge gap (s)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>min=0,max=5,by=.5</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
-      <c r="G90" t="n">
+      <c r="G92" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>highpass</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>highpass (low bound) Hz</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>min=10,max=40,by=5</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>Highpass for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>EMG periods</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>lowpass</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>lowpass (upper bound) Hz</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>min=30,max=120,by=5</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>Lowpass frequency for detecting EMG spectral power</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -3748,29 +3747,31 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>dBcriterion</t>
+          <t>highpass</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Use dB test</t>
+          <t>highpass (low bound) Hz</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>min=10,max=40,by=5</t>
+        </is>
+      </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Highpass for detecting EMG spectral power</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="94">
@@ -3781,12 +3782,12 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>lowpass</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Criterion (dB)</t>
+          <t>lowpass (upper bound) Hz</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
@@ -3796,16 +3797,16 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>min=-20,max=0,by=.5</t>
+          <t>min=30,max=120,by=5</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
+          <t>Lowpass frequency for detecting EMG spectral power</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>-6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
@@ -3816,12 +3817,12 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>doPsdSlope</t>
+          <t>dBcriterion</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Use slope test</t>
+          <t>Use dB test</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -3832,12 +3833,12 @@
       <c r="E95" s="1" t="n"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
+          <t>Flag an epoch when the interpolated signal has less power in the band than the recorded signal, by more than criterion dB</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3850,12 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>slopeCriterionAbsolute</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Slope above (dB/Hz)</t>
+          <t>Criterion (dB)</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -3864,18 +3865,16 @@
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>min=-2,max=2,by=.05</t>
+          <t>min=-20,max=0,by=.5</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
+          <t>An epoch has muscle activity in a channel when its interpolated signal has this many dB less power in the band than the recorded signal</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="97">
@@ -3886,32 +3885,28 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>slopeCriterionInterpolationDelta</t>
+          <t>doPsdSlope</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Slope minus interp. (dB/Hz)</t>
+          <t>Use slope test</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>min=-2,max=2,by=.05</t>
-        </is>
-      </c>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="n"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
+          <t>Flag an epoch when the spectrum in the band is flat or rising (slope above slopeCriterionAbsolute) AND flatter than its interpolation (slope difference beyond slopeCriterionInterpolationDelta). Combined with the dB test by OR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3923,28 +3918,32 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>zP</t>
+          <t>slopeCriterionAbsolute</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Use z-score p-value threshold</t>
+          <t>Slope above (dB/Hz)</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="E98" s="1" t="n"/>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>min=-2,max=2,by=.05</t>
+        </is>
+      </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
+          <t>Least-squares slope of the recorded spectrum in the band. Clean EEG falls (median about -0.3 dB/Hz at 20-40 Hz); muscle activity flattens it towards 0. Tested: 0 missed a burst whose epochs had slopes of -0.10 and +0.06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.1</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3955,12 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>zPvalue</t>
+          <t>slopeCriterionInterpolationDelta</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>p-value below</t>
+          <t>Slope minus interp. (dB/Hz)</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
@@ -3971,17 +3970,17 @@
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>min=.0001,max=.05,by=.0001</t>
+          <t>min=-2,max=2,by=.05</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
+          <t>Recorded slope minus the slope of the interpolated signal. Positive: flag when the recording is flatter by more than this; negative: flag when it is steeper by more than this</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3992,12 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>zFDR</t>
+          <t>zP</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Use z-score FDR threshold</t>
+          <t>Use z-score p-value threshold</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -4009,7 +4008,7 @@
       <c r="E100" s="1" t="n"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs whose one-sided p-value is below the threshold. Uncorrected: the more channels and epochs, the more chance flags</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4026,12 +4025,12 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>zFDRalpha</t>
+          <t>zPvalue</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>FDR q</t>
+          <t>p-value below</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -4041,123 +4040,123 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=.0001,max=.05,by=.0001</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>False discovery rate (q) for the z-score FDR threshold</t>
+          <t>Flag an epoch in a channel when P(Z &gt;= z) is below this (0.001 is about z = 3.1)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>zFDR</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Use z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="n"/>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>Z-score the band power (dB) per channel across all epochs and flag epochs that are significantly high after Benjamini-Hochberg FDR over all channels x epochs. Adapts to how many channels and epochs are tested</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>EMG periods</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>zFDRalpha</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>FDR q</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>min=.001,max=.1,by=.001</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>False discovery rate (q) for the z-score FDR threshold</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
           <t>flat periods</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>epochlen</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Epoch length (s)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>min=.05,max=2,by=.05</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
-      <c r="G102" t="n">
+      <c r="G104" t="n">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>overlap</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Epoch overlap (prop.)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>min=0,max=.9,by=.1</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>flat periods</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>maxbadtime</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Max. bad time (prop.)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>min=.05,max=.8,by=.05</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>0.3</v>
       </c>
     </row>
     <row r="105">
@@ -4168,12 +4167,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4183,16 +4182,16 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="106">
@@ -4203,12 +4202,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SD below (uV)</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4218,32 +4217,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>min=.05,max=5,by=.05</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>An epoch is flat in a channel when its detrended SD is below this</t>
+          <t>A channel that is flat in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>epochlen</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Epoch length (s)</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4253,12 +4252,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>min=.5,max=10,by=.5</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Length of the epochs the data are cut into</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -4268,17 +4267,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>excessive periods</t>
+          <t>flat periods</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>overlap</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Epoch overlap (prop.)</t>
+          <t>SD below (uV)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4288,16 +4287,16 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>min=0,max=.9,by=.1</t>
+          <t>min=.05,max=5,by=.05</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Proportion of overlap between successive epochs</t>
+          <t>An epoch is flat in a channel when its detrended SD is below this</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="109">
@@ -4308,12 +4307,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4323,16 +4322,16 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4343,12 +4342,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4358,16 +4357,16 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111">
@@ -4378,12 +4377,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FDR alpha</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4393,16 +4392,16 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>min=.001,max=.1,by=.001</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
+          <t>A channel that is excessive in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="112">
@@ -4413,12 +4412,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>maxamp</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Max. amplitude (uV)</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4428,69 +4427,67 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>min=50,max=2000,by=50</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>FDR alpha</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>dropdown</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>"Leave-one-out,RANSAC,Autoreject"</t>
+          <t>min=.001,max=.1,by=.001</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Leave-one-out</t>
-        </is>
+          <t>An epoch is excessive when its SD is unusually high for that channel, at this FDR corrected p</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>interpolation clean</t>
+          <t>excessive periods</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>epochlen</t>
+          <t>maxamp</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Epoch length (s)</t>
+          <t>Max. amplitude (uV)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4500,16 +4497,16 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>min=.5,max=10,by=.5</t>
+          <t>min=50,max=2000,by=50</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Length of the epochs the data are cut into</t>
+          <t>An epoch is excessive when the mean-centred signal exceeds this amplitude</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115">
@@ -4520,31 +4517,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>overlap</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Epoch overlap (prop.)</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>dropdown</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>min=0,max=.9,by=.1</t>
+          <t>"Leave-one-out,RANSAC,Autoreject"</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Proportion of overlap between successive epochs</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>0.5</v>
+          <t>Leave-one-out: each channel is compared with its spherical-spline prediction from all other channels. RANSAC: the same tests, with the prediction the median over random channel subsets (as PREP), robust against other bad channels nearby. Autoreject (Jas et al. 2017): per-channel peak-to-peak thresholds learned by cross-validation; bad channels are interpolated within an epoch and epochs with too many bad channels are removed. Autoreject uses Epoch length (no overlap), Merge gap and its folds setting only</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Leave-one-out</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -4555,12 +4554,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>maxbadtime</t>
+          <t>epochlen</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Max. bad time (prop.)</t>
+          <t>Epoch length (s)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4570,16 +4569,16 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>min=.05,max=.8,by=.05</t>
+          <t>min=.5,max=10,by=.5</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
+          <t>Length of the epochs the data are cut into</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -4590,12 +4589,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>mergegap</t>
+          <t>overlap</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Merge gap (s)</t>
+          <t>Epoch overlap (prop.)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4605,16 +4604,16 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>min=0,max=5,by=.5</t>
+          <t>min=0,max=.9,by=.1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
+          <t>Proportion of overlap between successive epochs</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="118">
@@ -4625,12 +4624,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sdcrit</t>
+          <t>maxbadtime</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SD of difference</t>
+          <t>Max. bad time (prop.)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4640,16 +4639,16 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>min=2,max=30,by=1</t>
+          <t>min=.05,max=.8,by=.05</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+          <t>A channel that differs from its interpolation in more than this proportion of the epochs is removed. While more than this proportion of the recording would still be removed, the noisiest remaining channel that reduces it is removed too</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="119">
@@ -4660,12 +4659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>rcrit</t>
+          <t>mergegap</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Min. correlation r</t>
+          <t>Merge gap (s)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4675,12 +4674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>min=-1,max=.9,by=.05</t>
+          <t>min=0,max=5,by=.5</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+          <t>Removed periods closer together than this are joined, and any stretch of data shorter than this between removed periods, boundary events or the start/end of the recording is removed too</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -4695,12 +4694,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ransac_draws</t>
+          <t>sdcrit</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RANSAC random subsets</t>
+          <t>SD of difference</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4710,18 +4709,16 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>min=10,max=200,by=10</t>
+          <t>min=2,max=30,by=1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>An epoch is bad when the SD of recorded minus interpolated signal exceeds this many times the median</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="121">
@@ -4732,12 +4729,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ransac_fraction</t>
+          <t>rcrit</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RANSAC subset fraction</t>
+          <t>Min. correlation r</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4747,18 +4744,16 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>min=.1,max=.5,by=.05</t>
+          <t>min=-1,max=.9,by=.05</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+          <t>An epoch is bad when the recorded and interpolated signal correlate below this</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4769,12 +4764,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ar_folds</t>
+          <t>ransac_draws</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Autoreject folds</t>
+          <t>RANSAC random subsets</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4784,34 +4779,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>min=3,max=20,by=1</t>
+          <t>min=10,max=200,by=10</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
+          <t>Only with Prediction RANSAC: number of random channel subsets the prediction is the median over (PREP: 50)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>task periods</t>
+          <t>interpolation clean</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>ransac_fraction</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seconds before event</t>
+          <t>RANSAC subset fraction</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4821,52 +4816,126 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>min=0,max=60,by=.5</t>
+          <t>min=.1,max=.5,by=.05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+          <t>Only with Prediction RANSAC: size of each random subset as a proportion of the channels (PREP: 0.25)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>interpolation clean</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ar_folds</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Autoreject folds</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>min=3,max=20,by=1</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Only with Method Autoreject: number of cross-validation folds used to learn the thresholds and the number of channels to interpolate or the share of bad channels that drops an epoch (autoreject: 10)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>task periods</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Seconds before event</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>min=0,max=60,by=.5</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Start of a task period, in seconds before each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>task periods</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Seconds after event</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>min=0,max=600,by=.5</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>End of a task period, in seconds after each event. Asked when you press Remove task or Remove no-task; batch uses the last answer</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>2</t>
         </is>
